--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -221,61 +221,61 @@
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -673,10 +673,6 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -734,26 +730,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>最高折扣</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>折实总价 (港币)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>折实呎价 (港币/呎)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>付款办法</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -789,7 +765,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -800,22 +776,6 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>60084800</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>44474</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -866,26 +826,6 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -921,7 +861,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2022-07-20</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -932,22 +872,6 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>32177500</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>36154</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -983,7 +907,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -994,22 +918,6 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>24596400</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>35907</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1060,26 +968,6 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -1115,7 +1003,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1126,22 +1014,6 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>31500000</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>35354</v>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1177,7 +1049,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1188,22 +1060,6 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>10751600</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>31255</v>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1254,26 +1110,6 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1324,26 +1160,6 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -1394,26 +1210,6 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1460,22 +1256,6 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>25096150</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>40218</v>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1526,26 +1306,6 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1592,22 +1352,6 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>12186144</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>35322</v>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1654,22 +1398,6 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>10909800</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>36006</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1720,26 +1448,6 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1775,7 +1483,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1786,22 +1494,6 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>13881480</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>31838</v>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1852,26 +1544,6 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1918,22 +1590,6 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>24577450</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>39387</v>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1984,26 +1640,6 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2050,22 +1686,6 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>11947200</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>34630</v>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2101,7 +1721,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2112,22 +1732,6 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>9712900</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>31950</v>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2178,26 +1782,6 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2248,26 +1832,6 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -2318,26 +1882,6 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2373,7 +1917,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2384,22 +1928,6 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>21323900</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>34173</v>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2450,26 +1978,6 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2505,7 +2013,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2516,22 +2024,6 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>10604600</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>30738</v>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2567,7 +2059,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2578,22 +2070,6 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>9616900</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>31739</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2644,26 +2120,6 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2699,7 +2155,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2710,22 +2166,6 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>13121400</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>30095</v>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2772,22 +2212,6 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>9247300</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>34764</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2823,7 +2247,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2834,22 +2258,6 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>20622700</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>33049</v>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2896,22 +2304,6 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>8940450</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>35199</v>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2958,22 +2350,6 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>11678350</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>33850</v>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3009,7 +2385,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3020,22 +2396,6 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>9456200</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>31106</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3086,26 +2446,6 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3141,7 +2481,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3152,22 +2492,6 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>13016900</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>29855</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3214,22 +2538,6 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>9085800</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>34157</v>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3265,7 +2573,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3276,22 +2584,6 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>10423500</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>30301</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3327,7 +2619,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3338,22 +2630,6 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>10318100</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>30527</v>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3400,22 +2676,6 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>8537650</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>34015</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3462,22 +2722,6 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>11438000</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>33154</v>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3513,7 +2757,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3524,22 +2768,6 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>9242000</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>30401</v>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3590,26 +2818,6 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3645,7 +2853,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3656,22 +2864,6 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>13619700</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>31238</v>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3718,22 +2910,6 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>9013600</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>33886</v>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3769,7 +2945,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2022-06-19</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3780,22 +2956,6 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>10340200</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>30059</v>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3842,22 +3002,6 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>11440850</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>33849</v>
-      </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3904,22 +3048,6 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>8455950</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>33689</v>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3966,22 +3094,6 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>11381950</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>32991</v>
-      </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4017,7 +3129,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4028,22 +3140,6 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>8960700</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>29573</v>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4094,26 +3190,6 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4160,22 +3236,6 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>14304150</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>32808</v>
-      </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N55" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4222,22 +3282,6 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>8941400</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>33614</v>
-      </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4284,22 +3328,6 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>11523500</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>33499</v>
-      </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N57" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4346,22 +3374,6 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>11407600</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>33750</v>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4408,22 +3420,6 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>8358100</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>33299</v>
-      </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N59" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4470,22 +3466,6 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>11314500</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>32796</v>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N60" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4521,7 +3501,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4532,22 +3512,6 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>8926700</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>29461</v>
-      </c>
-      <c r="M61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4598,26 +3562,6 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4653,7 +3597,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4664,22 +3608,6 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>12734700</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>29208</v>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4726,22 +3654,6 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>8941400</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>33614</v>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4777,7 +3689,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4788,22 +3700,6 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>10310500</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>30060</v>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4850,22 +3746,6 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>11407600</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>33750</v>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4912,22 +3792,6 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>8358100</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>33299</v>
-      </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4974,22 +3838,6 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>11314500</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>32796</v>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N68" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5025,7 +3873,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5036,22 +3884,6 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>8926700</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>29461</v>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5102,26 +3934,6 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5168,22 +3980,6 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>14232900</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>32644</v>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N71" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5230,22 +4026,6 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>8816000</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>33143</v>
-      </c>
-      <c r="M72" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5292,22 +4072,6 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>11453200</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>33294</v>
-      </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N73" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5343,7 +4107,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5354,22 +4118,6 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>10145600</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>30017</v>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5416,22 +4164,6 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>8153850</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>32485</v>
-      </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5478,22 +4210,6 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>11247050</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>32600</v>
-      </c>
-      <c r="M76" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N76" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5529,7 +4245,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5540,22 +4256,6 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="n">
-        <v>8859500</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>29239</v>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5606,26 +4306,6 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N78" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5672,22 +4352,6 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>14091350</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>32320</v>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N79" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5734,22 +4398,6 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>8753300</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>32907</v>
-      </c>
-      <c r="M80" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N80" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5785,7 +4433,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5796,22 +4444,6 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>10217000</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>29787</v>
-      </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N81" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5858,22 +4490,6 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="n">
-        <v>11305000</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>33447</v>
-      </c>
-      <c r="M82" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N82" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5920,22 +4536,6 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>8042700</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>32043</v>
-      </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N83" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5982,22 +4582,6 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>11175800</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>32394</v>
-      </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N84" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6033,7 +4617,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6044,22 +4628,6 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>8829800</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>29141</v>
-      </c>
-      <c r="M85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6110,26 +4678,6 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6176,22 +4724,6 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>14021050</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>32158</v>
-      </c>
-      <c r="M87" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N87" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6238,22 +4770,6 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>8481600</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>31886</v>
-      </c>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N88" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6300,22 +4816,6 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>11175800</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>32583</v>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6362,22 +4862,6 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>11065600</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>32738</v>
-      </c>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N90" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6424,22 +4908,6 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>7876450</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>31380</v>
-      </c>
-      <c r="M91" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N91" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6486,22 +4954,6 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>11153000</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>32328</v>
-      </c>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N92" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6537,7 +4989,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6548,22 +5000,6 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>29043</v>
-      </c>
-      <c r="M93" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N93" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6614,26 +5050,6 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6680,22 +5096,6 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>13949800</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>31995</v>
-      </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N95" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6742,22 +5142,6 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>8727650</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>32811</v>
-      </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N96" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6804,22 +5188,6 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="n">
-        <v>11029500</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>32062</v>
-      </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6866,22 +5234,6 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="n">
-        <v>10921200</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>32311</v>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6928,22 +5280,6 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="n">
-        <v>7764350</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>30934</v>
-      </c>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N99" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6994,26 +5330,6 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7060,22 +5376,6 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="n">
-        <v>10475650</v>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v>37016</v>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>360 日付款計劃</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7126,26 +5426,6 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7196,33 +5476,13 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -7386,7 +5646,7 @@
           <t>B | 1351呎 (4+房)
 $6008万
 $44,474/呎
-(22年-07月-05日)</t>
+(22年-07月-04日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr"/>
@@ -7415,7 +5675,7 @@
           <t>B | 685呎 (3房)
 $2460万
 $35,907/呎
-(23年-03月-24日)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -7423,7 +5683,7 @@
           <t>C | 890呎 (4+房)
 $3218万
 $36,154/呎
-(22年-07月-20日)</t>
+(22年-07月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr"/>
@@ -7459,7 +5719,7 @@
           <t>C | 344呎 (1房)
 $1075万
 $31,255/呎
-(24年-07月-11日)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -7467,7 +5727,7 @@
           <t>D | 891呎 (4+房)
 $3150万
 $35,354/呎
-(26年-03月-04日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -7486,7 +5746,7 @@
           <t>A | 436呎 (2房)
 $1388万
 $31,838/呎
-(26年-04月-28日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -7566,7 +5826,7 @@
           <t>C | 304呎 (1房)
 $971万
 $31,950/呎
-(26年-06月-18日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -7614,7 +5874,7 @@
           <t>A | 436呎 (2房)
 $1312万
 $30,095/呎
-(23年-12月-11日)</t>
+(23年-12月-10日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -7630,7 +5890,7 @@
           <t>C | 303呎 (1房)
 $962万
 $31,739/呎
-(22年-06月-24日)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -7638,7 +5898,7 @@
           <t>D | 345呎 (1房)
 $1060万
 $30,738/呎
-(22年-07月-13日)</t>
+(22年-07月-12日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -7654,7 +5914,7 @@
           <t>F | 624呎 (3房)
 $2132万
 $34,173/呎
-(22年-06月-29日)</t>
+(22年-06月-28日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -7678,7 +5938,7 @@
           <t>A | 436呎 (2房)
 $1302万
 $29,855/呎
-(22年-06月-30日)</t>
+(22年-06月-29日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -7694,7 +5954,7 @@
           <t>C | 304呎 (1房)
 $946万
 $31,106/呎
-(23年-06月-19日)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -7718,7 +5978,7 @@
           <t>F | 624呎 (3房)
 $2062万
 $33,049/呎
-(25年-05月-20日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -7742,7 +6002,7 @@
           <t>A | 436呎 (2房)
 $1362万
 $31,238/呎
-(24年-09月-26日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -7758,7 +6018,7 @@
           <t>C | 304呎 (1房)
 $924万
 $30,401/呎
-(23年-05月-18日)</t>
+(23年-05月-17日)</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -7782,7 +6042,7 @@
           <t>F | 338呎 (1房)
 $1032万
 $30,527/呎
-(22年-06月-17日)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -7790,7 +6050,7 @@
           <t>G | 344呎 (1房)
 $1042万
 $30,301/呎
-(22年-06月-17日)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
@@ -7829,7 +6089,7 @@
           <t>C | 303呎 (1房)
 $896万
 $29,573/呎
-(22年-06月-17日)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -7861,7 +6121,7 @@
           <t>G | 344呎 (1房)
 $1034万
 $30,059/呎
-(22年-06月-20日)</t>
+(22年-06月-19日)</t>
         </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
@@ -7884,7 +6144,7 @@
           <t>A | 436呎 (2房)
 $1273万
 $29,208/呎
-(22年-06月-24日)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -7900,7 +6160,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月-22日)</t>
+(22年-06月-21日)</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -7971,7 +6231,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月-17日)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -8003,7 +6263,7 @@
           <t>G | 343呎 (1房)
 $1031万
 $30,060/呎
-(22年-11月-17日)</t>
+(22年-11月-16日)</t>
         </is>
       </c>
       <c r="I15" s="25" t="inlineStr">
@@ -8042,7 +6302,7 @@
           <t>C | 303呎 (1房)
 $886万
 $29,239/呎
-(22年-07月-28日)</t>
+(22年-07月-27日)</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -8066,7 +6326,7 @@
           <t>F | 338呎 (1房)
 $1015万
 $30,017/呎
-(22年-07月-11日)</t>
+(22年-07月-10日)</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
@@ -8113,7 +6373,7 @@
           <t>C | 303呎 (1房)
 $883万
 $29,141/呎
-(22年-07月-05日)</t>
+(22年-07月-04日)</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -8145,7 +6405,7 @@
           <t>G | 343呎 (1房)
 $1022万
 $29,787/呎
-(24年-06月-18日)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
@@ -8184,7 +6444,7 @@
           <t>C | 303呎 (1房)
 $880万
 $29,043/呎
-(22年-06月-24日)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">

--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -221,61 +221,61 @@
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -730,6 +734,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -765,7 +789,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2022-07-04</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -776,6 +800,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>60084800</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>44474</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -826,6 +866,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -861,7 +921,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -872,6 +932,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>32177500</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>36154</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -907,7 +983,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -918,6 +994,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>24596400</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>35907</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -968,6 +1060,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1003,7 +1115,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1014,6 +1126,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>31500000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>35354</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1049,7 +1177,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1060,6 +1188,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>10751600</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>31255</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1110,6 +1254,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1160,6 +1324,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1210,6 +1394,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1256,6 +1460,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>25096150</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>40218</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1306,6 +1526,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1352,6 +1592,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>12186144</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>35322</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1398,6 +1654,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>10909800</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>36006</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1448,6 +1720,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1483,7 +1775,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1494,6 +1786,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>13881480</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>31838</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1544,6 +1852,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1590,6 +1918,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>24577450</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>39387</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1640,6 +1984,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1686,6 +2050,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>11947200</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>34630</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1721,7 +2101,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1732,6 +2112,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>9712900</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>31950</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1782,6 +2178,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1832,6 +2248,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1882,6 +2318,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1917,7 +2373,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1928,6 +2384,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>21323900</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>34173</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1978,6 +2450,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2013,7 +2505,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2024,6 +2516,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>10604600</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>30738</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2059,7 +2567,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2070,6 +2578,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>9616900</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>31739</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2120,6 +2644,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2155,7 +2699,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2166,6 +2710,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>13121400</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>30095</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2212,6 +2772,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>9247300</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>34764</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2247,7 +2823,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2258,6 +2834,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>20622700</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>33049</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2304,6 +2896,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>8940450</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>35199</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2350,6 +2958,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>11678350</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>33850</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2385,7 +3009,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2396,6 +3020,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>9456200</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>31106</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2446,6 +3086,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2481,7 +3141,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2492,6 +3152,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>13016900</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>29855</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2538,6 +3214,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>9085800</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>34157</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2573,7 +3265,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2584,6 +3276,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>10423500</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>30301</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2619,7 +3327,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2630,6 +3338,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>10318100</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>30527</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2676,6 +3400,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>8537650</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>34015</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2722,6 +3462,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>11438000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>33154</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2757,7 +3513,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2768,6 +3524,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>9242000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>30401</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2818,6 +3590,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2853,7 +3645,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2864,6 +3656,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>13619700</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>31238</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2910,6 +3718,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>9013600</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>33886</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2945,7 +3769,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2022-06-19</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2956,6 +3780,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>10340200</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>30059</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3002,6 +3842,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>11440850</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>33849</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3048,6 +3904,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>8455950</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>33689</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3094,6 +3966,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>11381950</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>32991</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3129,7 +4017,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3140,6 +4028,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>8960700</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>29573</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3190,6 +4094,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3236,6 +4160,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>14304150</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>32808</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3282,6 +4222,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>8941400</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>33614</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3328,6 +4284,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>11523500</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>33499</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3374,6 +4346,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>11407600</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>33750</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3420,6 +4408,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>8358100</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>33299</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3466,6 +4470,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>11314500</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>32796</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3501,7 +4521,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3512,6 +4532,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>8926700</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>29461</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3562,6 +4598,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3597,7 +4653,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3608,6 +4664,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>12734700</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>29208</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3654,6 +4726,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>8941400</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>33614</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3689,7 +4777,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3700,6 +4788,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>10310500</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>30060</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3746,6 +4850,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>11407600</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>33750</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3792,6 +4912,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>8358100</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>33299</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3838,6 +4974,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>11314500</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>32796</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3873,7 +5025,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3884,6 +5036,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>8926700</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>29461</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3934,6 +5102,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3980,6 +5168,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>14232900</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>32644</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4026,6 +5230,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>8816000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>33143</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4072,6 +5292,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>11453200</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>33294</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4107,7 +5343,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4118,6 +5354,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>10145600</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>30017</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4164,6 +5416,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>8153850</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>32485</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4210,6 +5478,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>11247050</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>32600</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4245,7 +5529,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4256,6 +5540,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>8859500</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>29239</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4306,6 +5606,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4352,6 +5672,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>14091350</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>32320</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4398,6 +5734,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>8753300</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>32907</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4433,7 +5785,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4444,6 +5796,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>10217000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>29787</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4490,6 +5858,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>11305000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>33447</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4536,6 +5920,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>8042700</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>32043</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4582,6 +5982,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>11175800</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>32394</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4617,7 +6033,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2022-07-04</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4628,6 +6044,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>8829800</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>29141</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4678,6 +6110,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4724,6 +6176,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>14021050</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>32158</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4770,6 +6238,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>8481600</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>31886</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4816,6 +6300,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>11175800</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>32583</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4862,6 +6362,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>11065600</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>32738</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4908,6 +6424,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>7876450</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>31380</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4954,6 +6486,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>11153000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>32328</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4989,7 +6537,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5000,6 +6548,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>29043</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5050,6 +6614,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5096,6 +6680,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>13949800</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>31995</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5142,6 +6742,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>8727650</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>32811</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5188,6 +6804,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>11029500</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>32062</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5234,6 +6866,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>10921200</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>32311</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5280,6 +6928,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>7764350</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>30934</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5330,6 +6994,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5376,6 +7060,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>10475650</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>37016</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>360 日付款計劃</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5426,6 +7126,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5476,13 +7196,33 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5646,7 +7386,7 @@
           <t>B | 1351呎 (4+房)
 $6008万
 $44,474/呎
-(22年-07月-04日)</t>
+(22年-07月-05日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr"/>
@@ -5675,7 +7415,7 @@
           <t>B | 685呎 (3房)
 $2460万
 $35,907/呎
-(23年-03月-23日)</t>
+(23年-03月-24日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -5683,7 +7423,7 @@
           <t>C | 890呎 (4+房)
 $3218万
 $36,154/呎
-(22年-07月-19日)</t>
+(22年-07月-20日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr"/>
@@ -5719,7 +7459,7 @@
           <t>C | 344呎 (1房)
 $1075万
 $31,255/呎
-(24年-07月-10日)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -5727,7 +7467,7 @@
           <t>D | 891呎 (4+房)
 $3150万
 $35,354/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -5746,7 +7486,7 @@
           <t>A | 436呎 (2房)
 $1388万
 $31,838/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -5826,7 +7566,7 @@
           <t>C | 304呎 (1房)
 $971万
 $31,950/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -5874,7 +7614,7 @@
           <t>A | 436呎 (2房)
 $1312万
 $30,095/呎
-(23年-12月-10日)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -5890,7 +7630,7 @@
           <t>C | 303呎 (1房)
 $962万
 $31,739/呎
-(22年-06月-23日)</t>
+(22年-06月-24日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -5898,7 +7638,7 @@
           <t>D | 345呎 (1房)
 $1060万
 $30,738/呎
-(22年-07月-12日)</t>
+(22年-07月-13日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -5914,7 +7654,7 @@
           <t>F | 624呎 (3房)
 $2132万
 $34,173/呎
-(22年-06月-28日)</t>
+(22年-06月-29日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -5938,7 +7678,7 @@
           <t>A | 436呎 (2房)
 $1302万
 $29,855/呎
-(22年-06月-29日)</t>
+(22年-06月-30日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -5954,7 +7694,7 @@
           <t>C | 304呎 (1房)
 $946万
 $31,106/呎
-(23年-06月-18日)</t>
+(23年-06月-19日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -5978,7 +7718,7 @@
           <t>F | 624呎 (3房)
 $2062万
 $33,049/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -6002,7 +7742,7 @@
           <t>A | 436呎 (2房)
 $1362万
 $31,238/呎
-(24年-09月-25日)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -6018,7 +7758,7 @@
           <t>C | 304呎 (1房)
 $924万
 $30,401/呎
-(23年-05月-17日)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -6042,7 +7782,7 @@
           <t>F | 338呎 (1房)
 $1032万
 $30,527/呎
-(22年-06月-16日)</t>
+(22年-06月-17日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -6050,7 +7790,7 @@
           <t>G | 344呎 (1房)
 $1042万
 $30,301/呎
-(22年-06月-16日)</t>
+(22年-06月-17日)</t>
         </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
@@ -6089,7 +7829,7 @@
           <t>C | 303呎 (1房)
 $896万
 $29,573/呎
-(22年-06月-16日)</t>
+(22年-06月-17日)</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -6121,7 +7861,7 @@
           <t>G | 344呎 (1房)
 $1034万
 $30,059/呎
-(22年-06月-19日)</t>
+(22年-06月-20日)</t>
         </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
@@ -6144,7 +7884,7 @@
           <t>A | 436呎 (2房)
 $1273万
 $29,208/呎
-(22年-06月-23日)</t>
+(22年-06月-24日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -6160,7 +7900,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月-21日)</t>
+(22年-06月-22日)</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -6231,7 +7971,7 @@
           <t>C | 303呎 (1房)
 $893万
 $29,461/呎
-(22年-06月-16日)</t>
+(22年-06月-17日)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -6263,7 +8003,7 @@
           <t>G | 343呎 (1房)
 $1031万
 $30,060/呎
-(22年-11月-16日)</t>
+(22年-11月-17日)</t>
         </is>
       </c>
       <c r="I15" s="25" t="inlineStr">
@@ -6302,7 +8042,7 @@
           <t>C | 303呎 (1房)
 $886万
 $29,239/呎
-(22年-07月-27日)</t>
+(22年-07月-28日)</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -6326,7 +8066,7 @@
           <t>F | 338呎 (1房)
 $1015万
 $30,017/呎
-(22年-07月-10日)</t>
+(22年-07月-11日)</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
@@ -6373,7 +8113,7 @@
           <t>C | 303呎 (1房)
 $883万
 $29,141/呎
-(22年-07月-04日)</t>
+(22年-07月-05日)</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -6405,7 +8145,7 @@
           <t>G | 343呎 (1房)
 $1022万
 $29,787/呎
-(24年-06月-17日)</t>
+(24年-06月-18日)</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
@@ -6444,7 +8184,7 @@
           <t>C | 303呎 (1房)
 $880万
 $29,043/呎
-(22年-06月-23日)</t>
+(22年-06月-24日)</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">

--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -3220,19 +3220,19 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>15057000</v>
+        <v>14304100</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>34534</v>
+        <v>32808</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6068,12 +6068,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 436呎 (2房)
-$1506万
-$34,534/呎
-(在售)</t>
+$1430万
+$32,808/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">

--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -1044,19 +1044,19 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>10751600</v>
+        <v>12649000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>31255</v>
+        <v>36770</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5714,12 +5714,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 344呎 (1房)
-$1075万
-$31,255/呎
-(24年-07月-10日)</t>
+$1265万
+$36,770/呎
+(在售)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">

--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -6073,7 +6073,7 @@
           <t>A | 436呎 (2房)
 $1430万
 $32,808/呎
-(26年-09月-29日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">

--- a/files/九龙-何文田-Prince Central.xlsx
+++ b/files/九龙-何文田-Prince Central.xlsx
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>24596400</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>35907</v>
+        <v>35960</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>31500000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>35354</v>
+        <v>35314</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>9712900</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>31950</v>
+        <v>32056</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>9456200</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>31106</v>
+        <v>31209</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>9242000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>30401</v>
+        <v>30502</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>10310500</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>30060</v>
+        <v>29972</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>10217000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>29787</v>
+        <v>29701</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>11764000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>34297</v>
+        <v>34198</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -5672,9 +5672,9 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 685呎 (3房)
+          <t>B | 684呎 (3房)
 $2460万
-$35,907/呎
+$35,960/呎
 (23年-03月-23日)</t>
         </is>
       </c>
@@ -5724,9 +5724,9 @@
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>D | 891呎 (4+房)
+          <t>D | 892呎 (4+房)
 $3150万
-$35,354/呎
+$35,314/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -5823,9 +5823,9 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $971万
-$31,950/呎
+$32,056/呎
 (26年-06月-17日)</t>
         </is>
       </c>
@@ -5951,9 +5951,9 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $946万
-$31,106/呎
+$31,209/呎
 (23年-06月-18日)</t>
         </is>
       </c>
@@ -6015,9 +6015,9 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $924万
-$30,401/呎
+$30,502/呎
 (23年-05月-17日)</t>
         </is>
       </c>
@@ -6260,9 +6260,9 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>G | 343呎 (1房)
+          <t>G | 344呎 (1房)
 $1031万
-$30,060/呎
+$29,972/呎
 (22年-11月-16日)</t>
         </is>
       </c>
@@ -6402,9 +6402,9 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>G | 343呎 (1房)
+          <t>G | 344呎 (1房)
 $1022万
-$29,787/呎
+$29,701/呎
 (24年-06月-17日)</t>
         </is>
       </c>
@@ -6473,9 +6473,9 @@
       </c>
       <c r="H18" s="25" t="inlineStr">
         <is>
-          <t>G | 343呎 (1房)
+          <t>G | 344呎 (1房)
 $1176万
-$34,297/呎
+$34,198/呎
 (已定价未售)</t>
         </is>
       </c>
